--- a/Correlation Master_Matrix.xlsx
+++ b/Correlation Master_Matrix.xlsx
@@ -1,26 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lisa.Crozier\Documents\Marine survival\Doug results\analyzeAKindices\LisaXP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lisa.Crozier\Documents\Marine survival\SEM-DFO-LisaXP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{055B4810-C563-47E4-9E50-BC8DFC9AE57A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B047FE3-E00B-42E1-B34E-1942AA1CFB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master_Matrix" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="DFA_Euph" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$J$1:$L$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Master_Matrix!$A$1:$BT$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet1!$J$1:$L$70</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -29,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="80">
   <si>
     <t>Variable_Name</t>
   </si>
@@ -267,11 +278,14 @@
   <si>
     <t>Growth</t>
   </si>
+  <si>
+    <t>abs_R</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -773,13 +787,15 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1134,7 +1150,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:BT70"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1367,7 +1384,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1585,7 +1602,7 @@
         <v>-0.84260716300000005</v>
       </c>
     </row>
-    <row r="3" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1803,7 +1820,7 @@
         <v>-0.74945024299999996</v>
       </c>
     </row>
-    <row r="4" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -2021,7 +2038,7 @@
         <v>-0.71088537399999996</v>
       </c>
     </row>
-    <row r="5" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -2239,7 +2256,7 @@
         <v>-0.86323176099999999</v>
       </c>
     </row>
-    <row r="6" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -2457,7 +2474,7 @@
         <v>-0.71462634999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2675,7 +2692,7 @@
         <v>-0.60763882999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -2893,7 +2910,7 @@
         <v>-0.74701668499999996</v>
       </c>
     </row>
-    <row r="9" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -3111,7 +3128,7 @@
         <v>-0.45565187000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -3329,7 +3346,7 @@
         <v>-0.46598103299999999</v>
       </c>
     </row>
-    <row r="11" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -3547,7 +3564,7 @@
         <v>-0.37849691400000002</v>
       </c>
     </row>
-    <row r="12" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -3765,7 +3782,7 @@
         <v>-0.38392965299999998</v>
       </c>
     </row>
-    <row r="13" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -3983,7 +4000,7 @@
         <v>-0.45486260099999998</v>
       </c>
     </row>
-    <row r="14" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -4201,7 +4218,7 @@
         <v>-0.47439656800000002</v>
       </c>
     </row>
-    <row r="15" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -4419,7 +4436,7 @@
         <v>-0.16849903099999999</v>
       </c>
     </row>
-    <row r="16" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -4637,7 +4654,7 @@
         <v>-0.25888263</v>
       </c>
     </row>
-    <row r="17" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -4855,7 +4872,7 @@
         <v>-0.21694727</v>
       </c>
     </row>
-    <row r="18" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -5073,7 +5090,7 @@
         <v>-0.322869988</v>
       </c>
     </row>
-    <row r="19" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -5291,7 +5308,7 @@
         <v>-6.7293775E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -5509,7 +5526,7 @@
         <v>-0.30005362099999999</v>
       </c>
     </row>
-    <row r="21" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -5727,7 +5744,7 @@
         <v>-0.234877106</v>
       </c>
     </row>
-    <row r="22" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -5945,7 +5962,7 @@
         <v>-6.9987509000000003E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -6163,7 +6180,7 @@
         <v>-0.27360593700000002</v>
       </c>
     </row>
-    <row r="24" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -6381,7 +6398,7 @@
         <v>-0.22173698</v>
       </c>
     </row>
-    <row r="25" spans="1:72" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:72" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>26</v>
       </c>
@@ -6599,7 +6616,7 @@
         <v>-0.166597831</v>
       </c>
     </row>
-    <row r="26" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -6817,7 +6834,7 @@
         <v>-0.13511606900000001</v>
       </c>
     </row>
-    <row r="27" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -7035,7 +7052,7 @@
         <v>-0.19578496500000001</v>
       </c>
     </row>
-    <row r="28" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -7253,7 +7270,7 @@
         <v>-0.202919454</v>
       </c>
     </row>
-    <row r="29" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -7471,7 +7488,7 @@
         <v>-0.31012710900000001</v>
       </c>
     </row>
-    <row r="30" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -7689,7 +7706,7 @@
         <v>-7.3849705000000002E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -7907,7 +7924,7 @@
         <v>7.4926730999999996E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -8125,7 +8142,7 @@
         <v>-0.11388749400000001</v>
       </c>
     </row>
-    <row r="33" spans="1:72" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:72" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>34</v>
       </c>
@@ -8343,7 +8360,7 @@
         <v>-0.10796460400000001</v>
       </c>
     </row>
-    <row r="34" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -8561,7 +8578,7 @@
         <v>0.10252038400000001</v>
       </c>
     </row>
-    <row r="35" spans="1:72" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:72" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>36</v>
       </c>
@@ -8779,7 +8796,7 @@
         <v>-6.7152719E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -8997,7 +9014,7 @@
         <v>-0.118106353</v>
       </c>
     </row>
-    <row r="37" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -9215,7 +9232,7 @@
         <v>-1.8712477000000002E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -9433,7 +9450,7 @@
         <v>0.181864846</v>
       </c>
     </row>
-    <row r="39" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -9651,7 +9668,7 @@
         <v>0.160185677</v>
       </c>
     </row>
-    <row r="40" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>41</v>
       </c>
@@ -9869,7 +9886,7 @@
         <v>0.101739318</v>
       </c>
     </row>
-    <row r="41" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>42</v>
       </c>
@@ -10087,7 +10104,7 @@
         <v>7.7558242999999999E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>43</v>
       </c>
@@ -10305,7 +10322,7 @@
         <v>0.12900246700000001</v>
       </c>
     </row>
-    <row r="43" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>44</v>
       </c>
@@ -10523,7 +10540,7 @@
         <v>0.13564305099999999</v>
       </c>
     </row>
-    <row r="44" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>45</v>
       </c>
@@ -10741,7 +10758,7 @@
         <v>0.14085238999999999</v>
       </c>
     </row>
-    <row r="45" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>46</v>
       </c>
@@ -10959,7 +10976,7 @@
         <v>0.13447072099999999</v>
       </c>
     </row>
-    <row r="46" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>47</v>
       </c>
@@ -11177,7 +11194,7 @@
         <v>0.15526343000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -11395,7 +11412,7 @@
         <v>0.162921121</v>
       </c>
     </row>
-    <row r="48" spans="1:72" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:72" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>49</v>
       </c>
@@ -11613,7 +11630,7 @@
         <v>0.20998702399999999</v>
       </c>
     </row>
-    <row r="49" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>50</v>
       </c>
@@ -11831,7 +11848,7 @@
         <v>0.27523161099999999</v>
       </c>
     </row>
-    <row r="50" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -12049,7 +12066,7 @@
         <v>0.12445545500000001</v>
       </c>
     </row>
-    <row r="51" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -12267,7 +12284,7 @@
         <v>0.197803854</v>
       </c>
     </row>
-    <row r="52" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -12485,7 +12502,7 @@
         <v>0.14786607399999999</v>
       </c>
     </row>
-    <row r="53" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>54</v>
       </c>
@@ -12703,7 +12720,7 @@
         <v>0.18329540799999999</v>
       </c>
     </row>
-    <row r="54" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>55</v>
       </c>
@@ -12921,7 +12938,7 @@
         <v>0.288972232</v>
       </c>
     </row>
-    <row r="55" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>56</v>
       </c>
@@ -13139,7 +13156,7 @@
         <v>0.121975243</v>
       </c>
     </row>
-    <row r="56" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>57</v>
       </c>
@@ -13357,7 +13374,7 @@
         <v>0.38272718999999999</v>
       </c>
     </row>
-    <row r="57" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>58</v>
       </c>
@@ -13575,7 +13592,7 @@
         <v>0.21564143499999999</v>
       </c>
     </row>
-    <row r="58" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>59</v>
       </c>
@@ -13793,7 +13810,7 @@
         <v>0.39905624299999998</v>
       </c>
     </row>
-    <row r="59" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>60</v>
       </c>
@@ -14011,7 +14028,7 @@
         <v>0.25130846400000001</v>
       </c>
     </row>
-    <row r="60" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>61</v>
       </c>
@@ -14229,7 +14246,7 @@
         <v>0.319209558</v>
       </c>
     </row>
-    <row r="61" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>62</v>
       </c>
@@ -14447,7 +14464,7 @@
         <v>0.16119427</v>
       </c>
     </row>
-    <row r="62" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>63</v>
       </c>
@@ -14665,7 +14682,7 @@
         <v>0.31155660200000002</v>
       </c>
     </row>
-    <row r="63" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>64</v>
       </c>
@@ -14883,7 +14900,7 @@
         <v>0.43812438999999997</v>
       </c>
     </row>
-    <row r="64" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>65</v>
       </c>
@@ -15101,7 +15118,7 @@
         <v>0.55078512000000002</v>
       </c>
     </row>
-    <row r="65" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>66</v>
       </c>
@@ -15319,7 +15336,7 @@
         <v>0.42095659099999999</v>
       </c>
     </row>
-    <row r="66" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>67</v>
       </c>
@@ -15537,7 +15554,7 @@
         <v>0.68416554299999999</v>
       </c>
     </row>
-    <row r="67" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>68</v>
       </c>
@@ -15973,7 +15990,7 @@
         <v>0.57097962400000002</v>
       </c>
     </row>
-    <row r="69" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>70</v>
       </c>
@@ -16191,7 +16208,7 @@
         <v>0.66675347900000004</v>
       </c>
     </row>
-    <row r="70" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>71</v>
       </c>
@@ -16410,12 +16427,1027 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:BT70" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="X12_DFA_biomassEuphShelfSum"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58933483-051F-4CA1-940A-350789EA23CD}">
+  <dimension ref="A1:G71"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="6">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7">
+        <f>ABS(B2)</f>
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="6">
+        <v>0.77360184600000004</v>
+      </c>
+      <c r="C3" s="7">
+        <f>ABS(B3)</f>
+        <v>0.77360184600000004</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0.77360184600000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="6">
+        <v>-0.72830536899999998</v>
+      </c>
+      <c r="C4" s="7">
+        <f>ABS(B4)</f>
+        <v>0.72830536899999998</v>
+      </c>
+      <c r="F4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0.65964222400000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="6">
+        <v>-0.70685881800000006</v>
+      </c>
+      <c r="C5" s="7">
+        <f>ABS(B5)</f>
+        <v>0.70685881800000006</v>
+      </c>
+      <c r="F5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0.61891766100000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7">
+        <v>-0.67486552899999996</v>
+      </c>
+      <c r="C6" s="7">
+        <f>ABS(B6)</f>
+        <v>0.67486552899999996</v>
+      </c>
+      <c r="F6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0.60341667300000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="7">
+        <v>0.65964222400000005</v>
+      </c>
+      <c r="C7" s="7">
+        <f>ABS(B7)</f>
+        <v>0.65964222400000005</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.58318347400000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="7">
+        <v>-0.64160396900000005</v>
+      </c>
+      <c r="C8" s="7">
+        <f>ABS(B8)</f>
+        <v>0.64160396900000005</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.57097962400000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="6">
+        <v>-0.63720983899999994</v>
+      </c>
+      <c r="C9" s="7">
+        <f>ABS(B9)</f>
+        <v>0.63720983899999994</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0.56224860200000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="7">
+        <v>0.61891766100000001</v>
+      </c>
+      <c r="C10" s="7">
+        <f>ABS(B10)</f>
+        <v>0.61891766100000001</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="7">
+        <v>0.55482597700000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="7">
+        <v>0.60341667300000001</v>
+      </c>
+      <c r="C11" s="7">
+        <f>ABS(B11)</f>
+        <v>0.60341667300000001</v>
+      </c>
+      <c r="F11" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0.52887675499999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="7">
+        <v>-0.59654344299999995</v>
+      </c>
+      <c r="C12" s="7">
+        <f>ABS(B12)</f>
+        <v>0.59654344299999995</v>
+      </c>
+      <c r="F12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" s="7">
+        <v>0.51989058700000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="7">
+        <v>-0.58349002699999997</v>
+      </c>
+      <c r="C13" s="7">
+        <f>ABS(B13)</f>
+        <v>0.58349002699999997</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="6">
+        <v>0.506387107</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7">
+        <v>-0.58349002699999997</v>
+      </c>
+      <c r="C14" s="7">
+        <f>ABS(B14)</f>
+        <v>0.58349002699999997</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0.49924137600000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="6">
+        <v>0.58318347400000003</v>
+      </c>
+      <c r="C15" s="7">
+        <f>ABS(B15)</f>
+        <v>0.58318347400000003</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="6">
+        <v>-0.55677367099999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="6">
+        <v>0.57097962400000002</v>
+      </c>
+      <c r="C16" s="7">
+        <f>ABS(B16)</f>
+        <v>0.57097962400000002</v>
+      </c>
+      <c r="F16" t="s">
+        <v>2</v>
+      </c>
+      <c r="G16" s="7">
+        <v>-0.58349002699999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="6">
+        <v>0.56224860200000004</v>
+      </c>
+      <c r="C17" s="7">
+        <f>ABS(B17)</f>
+        <v>0.56224860200000004</v>
+      </c>
+      <c r="F17" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="7">
+        <v>-0.58349002699999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="6">
+        <v>-0.55677367099999997</v>
+      </c>
+      <c r="C18" s="7">
+        <f>ABS(B18)</f>
+        <v>0.55677367099999997</v>
+      </c>
+      <c r="F18" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="7">
+        <v>-0.59654344299999995</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="7">
+        <v>0.55482597700000003</v>
+      </c>
+      <c r="C19" s="7">
+        <f>ABS(B19)</f>
+        <v>0.55482597700000003</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="6">
+        <v>-0.63720983899999994</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="7">
+        <v>0.52887675499999998</v>
+      </c>
+      <c r="C20" s="7">
+        <f>ABS(B20)</f>
+        <v>0.52887675499999998</v>
+      </c>
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="7">
+        <v>-0.64160396900000005</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="7">
+        <v>0.51989058700000002</v>
+      </c>
+      <c r="C21" s="7">
+        <f>ABS(B21)</f>
+        <v>0.51989058700000002</v>
+      </c>
+      <c r="F21" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" s="7">
+        <v>-0.67486552899999996</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="6">
+        <v>0.506387107</v>
+      </c>
+      <c r="C22" s="7">
+        <f>ABS(B22)</f>
+        <v>0.506387107</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="6">
+        <v>-0.70685881800000006</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="6">
+        <v>0.49924137600000001</v>
+      </c>
+      <c r="C23" s="7">
+        <f>ABS(B23)</f>
+        <v>0.49924137600000001</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G23" s="6">
+        <v>-0.72830536899999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="7">
+        <v>-0.49282287000000002</v>
+      </c>
+      <c r="C24" s="7">
+        <f>ABS(B24)</f>
+        <v>0.49282287000000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="7">
+        <v>-0.464568708</v>
+      </c>
+      <c r="C25" s="7">
+        <f>ABS(B25)</f>
+        <v>0.464568708</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="7">
+        <v>-0.46108019</v>
+      </c>
+      <c r="C26" s="7">
+        <f>ABS(B26)</f>
+        <v>0.46108019</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="7">
+        <v>-0.45312165599999998</v>
+      </c>
+      <c r="C27" s="7">
+        <f>ABS(B27)</f>
+        <v>0.45312165599999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="7">
+        <v>0.43260195699999998</v>
+      </c>
+      <c r="C28" s="7">
+        <f>ABS(B28)</f>
+        <v>0.43260195699999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="7">
+        <v>0.42420064800000001</v>
+      </c>
+      <c r="C29" s="7">
+        <f>ABS(B29)</f>
+        <v>0.42420064800000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" s="7">
+        <v>0.39070222900000001</v>
+      </c>
+      <c r="C30" s="7">
+        <f>ABS(B30)</f>
+        <v>0.39070222900000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="7">
+        <v>-0.38682519700000001</v>
+      </c>
+      <c r="C31" s="7">
+        <f>ABS(B31)</f>
+        <v>0.38682519700000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="7">
+        <v>0.38637965800000001</v>
+      </c>
+      <c r="C32" s="7">
+        <f>ABS(B32)</f>
+        <v>0.38637965800000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="7">
+        <v>-0.37955600900000003</v>
+      </c>
+      <c r="C33" s="7">
+        <f>ABS(B33)</f>
+        <v>0.37955600900000003</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="7">
+        <v>-0.358674771</v>
+      </c>
+      <c r="C34" s="7">
+        <f>ABS(B34)</f>
+        <v>0.358674771</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="7">
+        <v>-0.35634987899999998</v>
+      </c>
+      <c r="C35" s="7">
+        <f>ABS(B35)</f>
+        <v>0.35634987899999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="7">
+        <v>-0.35052240299999998</v>
+      </c>
+      <c r="C36" s="7">
+        <f>ABS(B36)</f>
+        <v>0.35052240299999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" s="7">
+        <v>-0.33520032999999999</v>
+      </c>
+      <c r="C37" s="7">
+        <f>ABS(B37)</f>
+        <v>0.33520032999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>26</v>
+      </c>
+      <c r="B38" s="7">
+        <v>0.317956515</v>
+      </c>
+      <c r="C38" s="7">
+        <f>ABS(B38)</f>
+        <v>0.317956515</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>20</v>
+      </c>
+      <c r="B39" s="7">
+        <v>0.31270342899999998</v>
+      </c>
+      <c r="C39" s="7">
+        <f>ABS(B39)</f>
+        <v>0.31270342899999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40" s="7">
+        <v>0.29445448099999999</v>
+      </c>
+      <c r="C40" s="7">
+        <f>ABS(B40)</f>
+        <v>0.29445448099999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" s="7">
+        <v>0.27202354400000001</v>
+      </c>
+      <c r="C41" s="7">
+        <f>ABS(B41)</f>
+        <v>0.27202354400000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" s="7">
+        <v>0.27073812800000002</v>
+      </c>
+      <c r="C42" s="7">
+        <f>ABS(B42)</f>
+        <v>0.27073812800000002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" s="7">
+        <v>0.26700017599999998</v>
+      </c>
+      <c r="C43" s="7">
+        <f>ABS(B43)</f>
+        <v>0.26700017599999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" s="7">
+        <v>-0.25882370799999999</v>
+      </c>
+      <c r="C44" s="7">
+        <f>ABS(B44)</f>
+        <v>0.25882370799999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45" s="7">
+        <v>-0.237588401</v>
+      </c>
+      <c r="C45" s="7">
+        <f>ABS(B45)</f>
+        <v>0.237588401</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46" s="7">
+        <v>0.236303657</v>
+      </c>
+      <c r="C46" s="7">
+        <f>ABS(B46)</f>
+        <v>0.236303657</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" s="7">
+        <v>-0.23562792199999999</v>
+      </c>
+      <c r="C47" s="7">
+        <f>ABS(B47)</f>
+        <v>0.23562792199999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48" s="7">
+        <v>-0.229278598</v>
+      </c>
+      <c r="C48" s="7">
+        <f>ABS(B48)</f>
+        <v>0.229278598</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>21</v>
+      </c>
+      <c r="B49" s="7">
+        <v>-0.211705158</v>
+      </c>
+      <c r="C49" s="7">
+        <f>ABS(B49)</f>
+        <v>0.211705158</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>17</v>
+      </c>
+      <c r="B50" s="7">
+        <v>0.20857429199999999</v>
+      </c>
+      <c r="C50" s="7">
+        <f>ABS(B50)</f>
+        <v>0.20857429199999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>63</v>
+      </c>
+      <c r="B51" s="7">
+        <v>0.20509321999999999</v>
+      </c>
+      <c r="C51" s="7">
+        <f>ABS(B51)</f>
+        <v>0.20509321999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>60</v>
+      </c>
+      <c r="B52" s="7">
+        <v>0.203038156</v>
+      </c>
+      <c r="C52" s="7">
+        <f>ABS(B52)</f>
+        <v>0.203038156</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" s="7">
+        <v>0.19228508999999999</v>
+      </c>
+      <c r="C53" s="7">
+        <f>ABS(B53)</f>
+        <v>0.19228508999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>31</v>
+      </c>
+      <c r="B54" s="7">
+        <v>-0.18860164800000001</v>
+      </c>
+      <c r="C54" s="7">
+        <f>ABS(B54)</f>
+        <v>0.18860164800000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>42</v>
+      </c>
+      <c r="B55" s="7">
+        <v>-0.175011584</v>
+      </c>
+      <c r="C55" s="7">
+        <f>ABS(B55)</f>
+        <v>0.175011584</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>43</v>
+      </c>
+      <c r="B56" s="7">
+        <v>-0.17484022199999999</v>
+      </c>
+      <c r="C56" s="7">
+        <f>ABS(B56)</f>
+        <v>0.17484022199999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>24</v>
+      </c>
+      <c r="B57" s="7">
+        <v>-0.16547477399999999</v>
+      </c>
+      <c r="C57" s="7">
+        <f>ABS(B57)</f>
+        <v>0.16547477399999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>51</v>
+      </c>
+      <c r="B58" s="7">
+        <v>0.15399645300000001</v>
+      </c>
+      <c r="C58" s="7">
+        <f>ABS(B58)</f>
+        <v>0.15399645300000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59" s="7">
+        <v>0.151102657</v>
+      </c>
+      <c r="C59" s="7">
+        <f>ABS(B59)</f>
+        <v>0.151102657</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60" s="7">
+        <v>-0.137535296</v>
+      </c>
+      <c r="C60" s="7">
+        <f>ABS(B60)</f>
+        <v>0.137535296</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>61</v>
+      </c>
+      <c r="B61" s="7">
+        <v>-0.135760353</v>
+      </c>
+      <c r="C61" s="7">
+        <f>ABS(B61)</f>
+        <v>0.135760353</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>23</v>
+      </c>
+      <c r="B62" s="7">
+        <v>-0.13337701099999999</v>
+      </c>
+      <c r="C62" s="7">
+        <f>ABS(B62)</f>
+        <v>0.13337701099999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>19</v>
+      </c>
+      <c r="B63" s="7">
+        <v>-0.11723937399999999</v>
+      </c>
+      <c r="C63" s="7">
+        <f>ABS(B63)</f>
+        <v>0.11723937399999999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>35</v>
+      </c>
+      <c r="B64" s="7">
+        <v>0.113315654</v>
+      </c>
+      <c r="C64" s="7">
+        <f>ABS(B64)</f>
+        <v>0.113315654</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>47</v>
+      </c>
+      <c r="B65" s="7">
+        <v>-9.6855108999999995E-2</v>
+      </c>
+      <c r="C65" s="7">
+        <f>ABS(B65)</f>
+        <v>9.6855108999999995E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" s="7">
+        <v>7.7921856999999997E-2</v>
+      </c>
+      <c r="C66" s="7">
+        <f>ABS(B66)</f>
+        <v>7.7921856999999997E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>30</v>
+      </c>
+      <c r="B67" s="7">
+        <v>-6.9551800999999996E-2</v>
+      </c>
+      <c r="C67" s="7">
+        <f>ABS(B67)</f>
+        <v>6.9551800999999996E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>68</v>
+      </c>
+      <c r="B68" s="7">
+        <v>-2.2446265999999999E-2</v>
+      </c>
+      <c r="C68" s="7">
+        <f>ABS(B68)</f>
+        <v>2.2446265999999999E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>62</v>
+      </c>
+      <c r="B69" s="7">
+        <v>-2.1658553000000001E-2</v>
+      </c>
+      <c r="C69" s="7">
+        <f>ABS(B69)</f>
+        <v>2.1658553000000001E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>44</v>
+      </c>
+      <c r="B70" s="7">
+        <v>8.2241569999999993E-3</v>
+      </c>
+      <c r="C70" s="7">
+        <f>ABS(B70)</f>
+        <v>8.2241569999999993E-3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>8</v>
+      </c>
+      <c r="B71" s="7">
+        <v>-4.2199830000000001E-3</v>
+      </c>
+      <c r="C71" s="7">
+        <f>ABS(B71)</f>
+        <v>4.2199830000000001E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F2:G23">
+    <sortCondition descending="1" ref="G2:G23"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:L70"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -18460,7 +19492,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="J1:L70">
+  <autoFilter ref="J1:L70" xr:uid="{00000000-0009-0000-0000-000001000000}">
     <filterColumn colId="1">
       <filters>
         <filter val="0.71950182"/>
